--- a/Resumo_atividade/Resumo-survey_os_20260910.xlsx
+++ b/Resumo_atividade/Resumo-survey_os_20260910.xlsx
@@ -1932,7 +1932,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
